--- a/Beaty_Company_Asset_Ledger.xlsx
+++ b/Beaty_Company_Asset_Ledger.xlsx
@@ -17,9 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_公司台账'!$A$1:$S$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_资产台账'!$A$1:$U$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_资产台账'!$A$1:$V$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_交易事件'!$A$1:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_关系映射'!$A$1:$F$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_关系映射'!$A$1:$F$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_估值锚点'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_信源与冲突'!$A$1:$C$10</definedName>
   </definedNames>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>本台账覆盖 Ross Beaty 历史以来创立/控制/参股的 20 家公司（A/B/C/D 四类）及对应 49 项核心矿权资产。</t>
+          <t>本台账覆盖 Ross Beaty 历史以来创立/控制/参股的 20 家公司（A/B/C/D 四类）及对应 59 项核心矿权资产。</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v1.0 · 2026-09-03 · 初版：20 家公司 / 49 项资产 / 16 笔交易事件 / 7 项估值锚点。</t>
+          <t>v1.1 · 2026-09-03 · 补全 3 家现公司（PAS/Equinox/Lumina Metals）资产组合：20 家公司 / 59 项资产 / 16 笔交易事件 / 7 项估值锚点。</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2531,7 +2531,8 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2632,10 +2633,15 @@
       </c>
       <c r="T1" s="2" t="inlineStr">
         <is>
+          <t>当前名下</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
           <t>证据等级</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2739,10 +2745,15 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Cargo Muchacho 山区中心）。Equinox Resources 曾持 47%（Hecla S-3/A 口径）或 50%（Hecla 10-K/A 与 Northern Miner 口径）权益，由合资伙伴 MK Gold Company 运营，为 Equinox 唯一在产资产。1994 年并入 Hecla 后成为 American Girl Mining Joint Venture（AGMJV = MK Gold + Hecla），1987-1996 运营，堆浸+选厂，1996 年金价低迷停产；Oro Cruz 项目区累计产金 &gt;710,000 oz（含 Cross 矿）。信源：https://d18rn0p25nwr6d.cloudfront.net/CIK-0000719413/f67b8f0d-0c12-432a-aa24-63fd37685061.pdf ; https://d18rn0p25nwr6d.cloudfront.net/CIK-0000719413/f4d74a09-0af0-4168-8a55-23cbedb25823.pdf ; https://www.northernminer.com/news/wheels-in-motion-for-merger-between-hecla-mining-and-equinox/1000178597 ; https://www.otcmarkets.com/file/company/financial-report/413752/content</t>
         </is>
@@ -2846,10 +2857,15 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似。Equinox 持有 100% 权益，是本次退出的核心驱动资产——Beaty 自述：「We had our big break by discovering a gold mine in Nevada called Rosebud, which ultimately led to the sale of Equinox in 1994」（Stratum International 访谈）。Equinox 投入 C$500 万推进，可研 1995 年底完成；Hecla 预计 1996 年底最早投产。1994 年被 Hecla 收购后，Hecla 1994 年黄金总产量指引由 6.1 万 oz 升至 13.1 万 oz。信源：https://stratum-international.com/interviews-with-mining-greats-ross-beaty/ ; https://d18rn0p25nwr6d.cloudfront.net/CIK-0000719413/f4d74a09-0af0-4168-8a55-23cbedb25823.pdf ; https://d18rn0p25nwr6d.cloudfront.net/CIK-0000719413/6a52f82d-7c80-40af-beda-0e68ab8c2e53.pdf ; https://www.northernminer.com/news/hecla-equinox-merger-approved/1000134903</t>
         </is>
@@ -2953,10 +2969,15 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Cargo Muchacho 山区中心，与 American Girl 同矿田）。Equinox 曾持有 Oro Cruz 项目——1994 年 Hecla 8-K 明确记载 Hecla 就「American Girl mine and Oro Cruz project of Equinox」的产量发行了总额 C$2,075,655 的产量票据（production notes），是 Equinox 持有该项目的 SEC 一手证据。项目含 Cross、American Girl、Padre y Madre、Queen 等氧化金矿点；AGMJV（MK Gold + Hecla）1987-1996 大规模露采+地下开采，1996 年底因金价崩塌关停并拆除设施；地下 2.4 km 主运平硐保存完好。现 Southern Empire 口径明确将其标注为「historical（历史）资源量」，非当前 NI 43-101。信源：https://d18rn0p25nwr6d.cloudfront.net/CIK-0000719413/f67b8f0d-0c12-432a-aa24-63fd37685061.pdf ; https://smp.gold/southern-empire-completes-its-acquisition-of-the-oro-cruz-project/ ; https://www.otcmarkets.com/file/company/financial-report/413752/content ; https://smp.gold?p=1008513/</t>
         </is>
@@ -3060,10 +3081,15 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（按「Novo Progresso 东南 70 km」推算，需以 Serabi 技术报告中的 UTM 坐标校正）。同口径资源量：Indicated 726 kt @ 8.4 g/t Au、17.0 g/t Ag（含金 195,000 oz、含银 396,000 oz）；Inferred 1,301 kt @ 4.3 g/t Au、5.1 g/t Ag（含金 181,000 oz、含银 215,000 oz）；合计资源含金 376,000 oz。2017 可研经济指标：税后 NPV US$31.0M（5% 折现）、剩余资本开支 US$28.8M、AISC US$783/oz、净现金运营成本 US$585/oz。Serabi 2024-04-16 更新口径：M&amp;I 795 kt @ 7.03 g/t Au（含金 179 koz）、Inferred 1,454 kt @ 5.81 g/t Au（含金 271 koz），3.16 g/t 边界品位（地下开采情景）。沿革：Tamin Mineração 1990 年圈定 → 2006-08 期权给 Chapleau Resources → 2009-09-01 Magellan Minerals 收购 Chapleau → 2016-05-09 Anfield 收购 Magellan Minerals → 2017-12-21 Anfield 售予 Serabi（总额 US$22.0M）。信源：https://www.globenewswire.com/news-release/2017/12/22/1269841/0/en/Serabi-Gold-plc-Completion-of-acquisition-of-the-Coringa-gold-project-Brazil.html ; https://stockhouse.com/news/press-releases/2017/11/14/serabi-gold-plc-conditional-acquisition-of-the-coringa-gold-project-brazil ; https://www.serabigold.com?p=33/ ; http://canadianminingreport.com/company_resource/180228_NI43-101_Serab_Cor_F.pdf</t>
         </is>
@@ -3167,10 +3193,15 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（矿区精确坐标未查到，行政区归属在不同信源间表述不一，需以 Mayaniquel 官网 mni.com.gt 与危地马拉能源矿产部矿权登记核实）。沿革：1998 年起 Jaguar Nickel 通过危地马拉子公司 Mayaniquel 在 Izabal 勘探镍并开发旗舰资产 Sechol 矿 → 2006 年 BHP Billiton 收购 Jaguar Nickel 取得 → 2009 年 BHP 将 Mayaniquel 售予 Anfield Nickel Corp.（即后来的 Anfield Gold Corp.）→ 2013 年取得 Sechol 采矿许可 → 2014-06-16 售予 Cunico Resources N.V.（原付款计划：2018 年底前每月 US$250,000 + 2019-06 一次性付款，按第五年镍均价公式约 US$1,200 万-1,900 万）→ 2017-11-10 Cunico 违约（9-11 月付款未付），Anfield 发出违约通知并与 International Nickel Supply SA 签有条件协议 → 2017-12-21 Anfield 完成对 Mayaniquel 股份止赎，随即转让 INS，共收 US$13.0M（2017-11 先收 US$0.5M + 交割 US$12.5M）。资源量/储量、品位、产能全部未查到，应查 SEDAR+ 上 Anfield Gold 2013-2016 年的 NI 43-101 技术报告与年报。信源：https://www.econotimes.com/Anfield-Gold-Announces-Default-of-Cunico-and-Enters-into-Agreement-with-International-Nickel-Supply-SA-1003107 ; https://www.einpresswire.com/article/422695361 ; https://pitchbook.com/profiles/company/154730-35 ; https://www.isaportal.org/resources/resource/entanglements-of-firm-size-and-country-of-origin-with-mining-company-reputational-risk-in-guatemala/download/ ; https://www.mining-journal.com/m-amp-a/news/1265337/anfield-pursues-alternate-nickel-sale</t>
         </is>
@@ -3274,10 +3305,15 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>坐标精度：Svartsengi 电站为精确坐标；Reykjanes 电站约 63.8256 / -22.6772。Magma Energy 收购路径：2009-07-23 签约购入 HS Orka 10.78%（并获约 5% 增持期权）→ 2009-09 再购 32.32%（对价约 US$2,950 万现金 + 约 US$6,880 万 7 年期债券，票息 1.52%，以所购股份质押）→ 2010 年 6 月 30 日时持股 46.18%，年后再购 52.35%，合计约 98.5%。该交易为 2008 年冰岛银行业危机后冰岛最大外资投资，引发冰岛社会反弹（歌手 Björk 于 2010-05-21 在 Reykjavík Grapevine 发公开信要求政府撤销与 Magma 的合同），但获冰岛政府批准。Beaty 时任 HS Orka 董事长。HS Orka 约 50% 电力销售与铝价部分挂钩（嵌入衍生品）。信源：http://en.wikipedia-on-ipfs.org/wiki/Alterra_Power ; https://www.energy-daily.com/reports/Magma_caps_09_with_Iceland_geothermal_win_999.html ; https://www.thinkgeoenergy.com/magma-energy-releases-financial-results-for-the-financial-year-2010/amp/ ; https://www.theglobeandmail.com/globe-investor/magma-steams-full-speed-ahead/article4285532/</t>
         </is>
@@ -3381,10 +3417,15 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Toba Inlet 流域中心）。East Toba 与 Montrose Creek 两座电站相距 18 km，2010 年投运；与 BC Hydro 签订至 2045 年的购电协议（EPA）。Upper Toba Valley 后续规划 124 MW（Jimmie Creek + Upper Toba River），2013 年获 BC Hydro 购电协议，Jimmie Creek 62 MW 于 2016 年达产（坐标 50.568962 / -124.072627）。信源：http://en.wikipedia-on-ipfs.org/wiki/Alterra_Power ; https://prod.wikiwand.com/en/articles/Magma_Energy ; https://www.nsenergybusiness.com/?p=1326</t>
         </is>
@@ -3488,10 +3529,15 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Dokie Ridge 一带，需以 Innergex 项目页或 BC 环境评估证书坐标核实）。2011 年 Magma 与 Plutonic 合并时 Alterra 已在 BC 拥有 1 座径流水电与 1 座风电场，Dokie 1 为其中的风电资产；Alterra 另有 Upper Toba Valley 水电开发权与安大略省太阳能项目期权。信源：http://en.wikipedia-on-ipfs.org/wiki/Alterra_Power ; https://prod.wikiwand.com/en/articles/Magma_Energy ; https://www.biv.com/news/resources-agriculture/innergex-buy-vancouvers-alterra-power-8251073</t>
         </is>
@@ -3595,10 +3641,15 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（德州北部 Floyd / Lubbock 县一带，需以 Innergex 项目页或美国 EIA 机组坐标核实）。Alterra 美国资产组合的重要组成；2011 年合并公告时描述为「an option on a solar project in Ontario」之外的美国风电持仓。另有 Kokomo 太阳能 7 MW（印第安纳州）。信源：http://en.wikipedia-on-ipfs.org/wiki/Alterra_Power ; https://prod.wikiwand.com/en/articles/Magma_Energy ; https://www.biv.com/news/resources-agriculture/innergex-buy-vancouvers-alterra-power-8251073</t>
         </is>
@@ -3702,10 +3753,15 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（密歇根州 Mason 县一带，需以 Innergex 项目页或美国 EIA 机组坐标核实）。Alterra 装机最小的美国风电资产。补注：Alterra 另有内华达州 Soda Lake 地热电站（Magma 起家资产，约 11-15 MW），已于 2015-01 售予 Cyrq Energy，故未单列资产行。信源：http://en.wikipedia-on-ipfs.org/wiki/Alterra_Power ; https://prod.wikiwand.com/en/articles/Magma_Energy ; https://www.thinkgeoenergy.com/tag/alterra-power-corp/</t>
         </is>
@@ -3809,10 +3865,15 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Galore Creek / Telegraph Creek 一带中心点，需以 MTB 官网项目页或 BC MINFILE 坐标核实）。面积 344-350 km²，为 Golden Triangle 最大土地包之一；位于 Galore Creek（Teck/Newmont）、Schaft Creek（Teck）、Saddle（Newmont）与在产 Red Chris（Newmont/Imperial Metals）四个世界级斑岩矿床之间，处于同一构造带。历史上曾被 50 多家公司分散持有、各自只盯小靶区，Dok 一带因横跨两个旧矿权边界而从未被系统勘探，MTB 是首家整合并系统勘探者；2023 年实施首次钻探。2024-2025 年策略转向铜-金斑岩，并引入 AI 地质建模精细定靶，目标是引入大型矿业公司 farm-in。合并时双方已启动 NI 43-101 报告编制，截至 2026-09 尚无公开资源量。信源：https://www.mtb-metals.com/news-releases/mtb-sells-surprise-creek-project-for-1-million/ ; https://www.proactiveinvestors.com.au/companies/news/1004224/ ; https://seekingalpha.com/pr/20270310-exgen-resources-and-mtb-metals-enter-into-arrangement-agreement-to-merge-creating-a-well ; https://resourceworld.com?p=96764/ ; https://www.bitget.org/en-AE/stock/tsxv-mtb/what-is</t>
         </is>
@@ -3916,10 +3977,15 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（以 Stewart 港为中心外推，需以 MTB 官网或 BC MINFILE 坐标核实）。以历史 Mountain Boy 银矿为核心，矿权区内有多个银、金、铜矿点；基础设施优越——公路可达，距深水不冻港 Stewart 约 20 km，显著降低未来资本开支。尚无 NI 43-101 资源量。信源：https://www.mtb-metals.com/news-releases/mtb-sells-surprise-creek-project-for-1-million/ ; https://www.bitget.org/en-AE/stock/tsxv-mtb/what-is ; https://www.proactiveinvestors.com.au/companies/news/1004224/</t>
         </is>
@@ -4023,10 +4089,15 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="V14" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（以 Stewart 地区为中心外推，需以 MTB 官网或 BC MINFILE 坐标核实）。182 个历史钻孔圈定银-铅-锌矿化带，距公路仅 4 km；公司认为仍存多个高品位银靶区待验证。尚无 NI 43-101 资源量。信源：https://www.mtb-metals.com/news-releases/mtb-sells-surprise-creek-project-for-1-million/ ; https://www.bitget.org/en-AE/stock/tsxv-mtb/what-is</t>
         </is>
@@ -4130,10 +4201,15 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（以 Stewart 地区为中心外推，需以 MTB 官网或 BC MINFILE 坐标核实）。为过去的金-铜生产矿，MTB 持有 35% 权益（与 Decade Resources 合资），临公路、物流便利；近期钻探见 2 m @ 26 g/t 金。尚无 NI 43-101 资源量。MTB 另有 Theia（银矿化带长 500 m，2020 年抓样达 39 kg/t 银即约 1,100 oz/t；另两带铜 &gt;5%）、Southmore（1980s-1990s 勘探后被遗忘，MTB 整合后航磁+野外工作确认多条金铜带，样品最高 20% Cu、35 g/t Au；Resource World 引 12.7% Cu + 29.4 g/t Au 样品）两个项目未单列资产行。信源：https://www.mtb-metals.com/news-releases/mtb-sells-surprise-creek-project-for-1-million/ ; https://resourceworld.com?p=96764/ ; https://www.proactiveinvestors.com.au/companies/news/1004224/</t>
         </is>
@@ -4237,10 +4313,15 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="V16" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Whitehorse 西北约 300 km，需以 2022 年技术报告坑口坐标校正）。【储量】P&amp;P 磨矿储量 1,217.1 Mt @ 0.19% Cu、0.22 g/t Au、0.021% Mo、1.7 g/t Ag + P&amp;P 堆浸储量 209.6 Mt @ 0.26 g/t Au、0.036% Cu、1.9 g/t Ag。【2022 可研经济指标】税前/税后 NPV C$23 亿（8% 折现）、税后 IRR 18.1%、3 年回本、前期资本 C$36.2 亿、维持资本 C$7.51 亿、C1 现金成本（副产品抵扣后）$(0.80)/lb Cu、剥采比 0.43:1、年均税后现金流 C$5.17 亿；价格假设 US$3.25/lb Cu、US$1,550/oz Au、US$12.00/lb Mo、US$22.00/oz Ag。【阶段】已完成 2022 可研，目前处于 YESAB（育空环境与社会经济评估委员会）Panel Review——育空最高级别环评，ESE 声明已于 2025-10 提交，流程含技术分析、公开听证与最终建议。【沿革】Casino 原由 Inco/其他方发现，经 Lumina Resources Corp.（Beaty 2005 年分拆四小龙之一）持有，2006 年 11 月随 Lumina 与 Western Copper 换股合并转入；Beaty 由此出任 Western Copper 联合董事长（2006-11 至 2009-09）。【股东】Rio Tinto 约 8.5%（投资者权利协议已延至 2026-11-30 或持股跌破 5%）、Mitsubishi Materials 5%；育空政府已投入 C$1.30 亿开建 100 km 进场道路。【经济影响】MNP 2025 年报告：建设+27 年运营+复垦合计为加拿大 GDP 贡献 C$441 亿。信源：https://www.westerncopperandgold.com/casino-project/ ; https://www.westerncopperandgold.com/wp-content/uploads/2025/12/Casino-Project-2022-Technical-Report-Feasibility-Study.pdf ; https://www.sec.gov/Archives/edgar/data/1364125/000106299326001628/exhibit99-1.htm ; https://www.northernminer.com/financing/western-copper-and-gold-raises-40m-for-casino-in-yukon/1003866422 ; https://casinomining.com/news/western-copper-and-lumina-resources-to-complete-business-combination-2/</t>
         </is>
@@ -4344,10 +4425,15 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Chalchihuites）；Beaty 任内原创旗舰资产；La Colorada Skarn（PEA 2023-12）另含 M&amp;I 265.4 Mt @ 36 g/t Ag + Inferred 61.7 Mt @ 30 g/t、达产年均 17.2 Moz Ag；信源 https://panamericansilver.com/operations/silver-segment/la-colorada-skarn/</t>
         </is>
@@ -4451,10 +4537,15 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t>坐标精确（29°00'N 108°32'W）；2012 并购 Minefinders 所得（Beaty 任董事长期间并购、非原创）；2025 年接近残浸结束；信源 https://panamericansilver.com/wp-content/uploads/2023/01/DoloresTR2022-06.pdf</t>
         </is>
@@ -4558,10 +4649,15 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="V19" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似；Beaty 任内长期旗舰资产（非并购所得）；信源 https://www.panamericansilver.com/operations/south-america/huaron</t>
         </is>
@@ -4665,10 +4761,15 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似；M&amp;I 1.0 Mt（0.7 Mt @ 183 + 0.3 Mt @ 174 g/t）+ Inferred 1.6 Mt @ 171 g/t（8.7 Moz）；P&amp;P 吨位品位未查到；Beaty 任内资产；信源 https://panamericansilver.com/?p=94</t>
         </is>
@@ -4772,10 +4873,15 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Gobernador Gregores 一带）；Beaty 任内开发投产（2006 获批建设）；2022 停产转闭坑；信源 https://panamericansilver.com/?p=95/</t>
         </is>
@@ -4849,42 +4955,47 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>银 632.4 Moz、铅 1</t>
+          <t>银 632.4 Moz、铅 1,326 kt、铜 71 kt（Inferred 另 45.9 Mt @ 81 g/t Ag → 119.4 Moz Ag）</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>326 kt、铜 71 kt（Inferred 另 45.9 Mt @ 81 g/t Ag → 119.4 Moz Ag）</t>
+          <t>未开发（PEA 预计前 5 年 ~19.8 Moz Ag/年）</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>未开发（PEA 预计前 5 年 ~19.8 Moz Ag/年）</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>Pan American Silver（100%，Minera Argenta）</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Pan American Silver（100%，Minera Argenta）</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
           <t>一手</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>坐标精确（42°24'54"S 68°49'12"W）；2010 收购；因 Chubut 省 Law 5001 禁露天/氰化而搁置；Beaty 任内（董事长至 2021）收购；信源 https://panamericansilver.com/?p=96/</t>
         </is>
       </c>
     </row>
@@ -4986,10 +5097,15 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="V23" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（San Rafael Las Flores）；2019 并购 Tahoe Resources 所得（非 Beaty 原创、并购所得）；2017 年因最高法院咨询令暂停；信源 https://panamericansilver.com/?p=18572/</t>
         </is>
@@ -5059,42 +5175,47 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>金 1</t>
+          <t>金 1,660 koz（M&amp;I 另 18.12 Mt @ 1.49 g/t → 868 koz）</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>660 koz（M&amp;I 另 18.12 Mt @ 1.49 g/t → 868 koz）</t>
+          <t>~70-115 koz Au/年（2025 指引 70-90 koz）</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>~70-115 koz Au/年（2025 指引 70-90 koz）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>洛阳钼业（CMOC，2025-12 公告收购、2026 年初交割）</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>洛阳钼业（CMOC，2025-12 公告收购、2026 年初交割）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
           <t>一手</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Godofredo Viana）；Beaty 组建时带来（Trek Mining，2017-12 三合一组建）；2025-12 洛阳钼业以 10.15 亿美元收购巴西资产（含 Aurizona）；信源 https://en.cmoc.com/html/2025/News_1215/82.html 及 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
       </c>
     </row>
@@ -5162,42 +5283,47 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>金 763 koz（M&amp;I 另 21.4 Mt @ 2.21 g/t → 1</t>
+          <t>金 763 koz（M&amp;I 另 21.4 Mt @ 2.21 g/t → 1,524 koz）</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>524 koz）</t>
+          <t>~65 koz Au/年（2025 指引 12.5-14.5 万盎司为 Bahia 综合体合计）</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>~65 koz Au/年（2025 指引 12.5-14.5 万盎司为 Bahia 综合体合计）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>洛阳钼业（CMOC，2025-12 公告、2026 年初交割）</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>洛阳钼业（CMOC，2025-12 公告、2026 年初交割）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
           <t>一手</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Barrocas/Santa Luz 一带）；并购所得（2020-03 Leagold 合并、原 Brio Gold）；累计产金已超 330 万盎司；信源 https://www.equinoxgold.com/news/equinox-gold-extends-fazenda-mine-life-by-seven-years-with-updated-mineral-reserve-and-mineral-resource-estimate/</t>
         </is>
       </c>
     </row>
@@ -5295,10 +5421,15 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Riacho dos Machados）；并购所得（2020-03 Leagold 合并、原 Brio Gold）；信源 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
@@ -5368,42 +5499,47 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>金 1</t>
+          <t>金 1,191 koz（M&amp;I 含储量；Inferred 另 20.40 Mt @ 3.21 g/t → 2,108 koz）</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>191 koz（M&amp;I 含储量；Inferred 另 20.40 Mt @ 3.21 g/t → 2</t>
+          <t>~3,500-4,500 tpd 选厂（地下开采）</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>108 koz）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>~3,500-4,500 tpd 选厂（地下开采）</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>2018-05-31</t>
+          <t>Pilar Gold Inc.（2021-04 自 Equinox 收购）</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Pilar Gold Inc.（2021-04 自 Equinox 收购）</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Pilar de Goiás）；并购所得（2020-03 Leagold 合并）后于 2021-04 出售予 Pilar Gold Inc.；现非 Equinox 资产；信源 https://versamet.com/?p=416</t>
         </is>
       </c>
     </row>
@@ -5471,42 +5607,47 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>金 1</t>
+          <t>金 1,075 koz（M&amp;I 另 16.58 Mt @ 1.69 g/t → 900 koz）</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>075 koz（M&amp;I 另 16.58 Mt @ 1.69 g/t → 900 koz）</t>
+          <t>~75 koz Au/年（2025 指引 12.5-14.5 万盎司为 Bahia 综合体合计）</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>~75 koz Au/年（2025 指引 12.5-14.5 万盎司为 Bahia 综合体合计）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>洛阳钼业（CMOC，2025-12 公告、2026 年初交割）</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>洛阳钼业（CMOC，2025-12 公告、2026 年初交割）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
           <t>一手</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似；并购所得（2020-03 Leagold 合并、原 Brio Gold）；曾停产后重启；信源 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
       </c>
     </row>
@@ -5578,42 +5719,47 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>金 5</t>
+          <t>金 5,354 koz（M&amp;I 另 325.33 Mt @ 0.75 g/t → 7,897 koz）</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>354 koz（M&amp;I 另 325.33 Mt @ 0.75 g/t → 7</t>
+          <t>~160 koz Au/年（2024）</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>897 koz）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>~160 koz Au/年（2024）</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold（100%）</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Mezcala）；并购所得（2020-03 Leagold 合并）；曾因社区封锁间歇停产；信源 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
       </c>
     </row>
@@ -5681,42 +5827,47 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>金 4</t>
+          <t>金 4,168 koz（M&amp;I 另 74.23 Mt @ 0.62 g/t → 1,470 koz）</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>168 koz（M&amp;I 另 74.23 Mt @ 0.62 g/t → 1</t>
+          <t>Phase 1 设计 ~30-40 koz Au/年（Phase 2 后可达 ~200 koz/年）</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>470 koz）</t>
+          <t>建设</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>Phase 1 设计 ~30-40 koz Au/年（Phase 2 后可达 ~200 koz/年）</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>建设</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold（100%）</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（San Bernardino County）；Beaty 组建时带来（NewCastle Gold，2017-12）；2024-08 Phase 1 暂停以推进 Phase 2 许可；信源 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
       </c>
     </row>
@@ -5784,42 +5935,47 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>金 471 koz（M&amp;I 另 104.99 Mt @ 0.41 g/t → 1</t>
+          <t>金 471 koz（M&amp;I 另 104.99 Mt @ 0.41 g/t → 1,384 koz）</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>384 koz）</t>
+          <t>~85-95 koz Au/年（2025 指引，历史 2019 年 125.7 koz）</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>~85-95 koz Au/年（2025 指引，历史 2019 年 125.7 koz）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold（100%）</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t>一手</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Imperial County）；并购所得（2018-10 自 New Gold 以 1.58 亿美元收购，非 NewCastle）；信源 https://www.equinoxgold.com/?p=1548</t>
         </is>
       </c>
     </row>
@@ -5887,42 +6043,47 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>金 5</t>
+          <t>金 5,700 koz（地下 M&amp;I 另 29.97 Mt @ 2.30 g/t → 2,218 koz）</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>700 koz（地下 M&amp;I 另 29.97 Mt @ 2.30 g/t → 2</t>
+          <t>~400 koz Au/年（前 5 年，2025 指引 220-260 koz）</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>218 koz）</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>~400 koz Au/年（前 5 年，2025 指引 220-260 koz）</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold（100%）</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Geraldton）；并购所得（2021 收购 Premier Gold 获 60%，2024-05 购 Orion 40% 至 100%）；2024-05-22 首金；信源 https://www.slideshare.net/slideshow/equinox-gold-corporate-presentation-october-2024/272635658</t>
         </is>
       </c>
     </row>
@@ -6020,10 +6181,15 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t>坐标精度：近似（Valentine Lake 一带）；并购所得（原 Marathon Gold → Calibre 2024 → Equinox 2025-06 合并 Calibre 获得）；2025 年首金/2025-11 商业生产；信源 https://www.equinoxgold.com/?p=6571/</t>
         </is>
@@ -6097,42 +6263,47 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>金 2</t>
+          <t>金 2,321 koz、银 12.8 Moz、铜 93 Mlb（Inferred 另 224.3 Mt @ 0.60 g/t Au → 金 4,313 koz、银 18.1 Moz）</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>321 koz、银 12.8 Moz、铜 93 Mlb（Inferred 另 224.3 Mt @ 0.60 g/t Au → 金 4</t>
+          <t>PEA 2021（Condor North：12 年、187 koz Au + 758 koz Ag/年）</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>313 koz、银 18.1 Moz）</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>PEA 2021（Condor North：12 年、187 koz Au + 758 koz Ag/年）</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>Silvercorp Metals（98.7%，经 Luminex→Adventus→Silvercorp 2024-07 收购）</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>否</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>Silvercorp Metals（98.7%，经 Luminex→Adventus→Silvercorp 2024-07 收购）</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Fruta del Norte 南 ~35 km）；Luminex 旗舰资产（Beaty 主要股东 19.9%）；2023-11 Adventus 以 0.67 股/股换股合并、2024-07 Silvercorp 收购 Adventus；信源 https://www.newswire.ca/en/releases/archive/February2022/09/c4386.html</t>
         </is>
       </c>
     </row>
@@ -6234,12 +6405,17 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t>坐标精度：近似（Pegasus A 距 Estero Hondo 南 2 km、Pegasus B 邻 Salazar Curipamba）；无已披露资源量（资源量未查到）；2018 Anglo 赚入（承诺投入 ~5</t>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Pegasus A 距 Estero Hondo 南 2 km、Pegasus B 邻 Salazar Curipamba）；无已披露资源量（资源量未查到）；2018 Anglo 赚入（承诺投入 ~5,730 万美元）；信源 https://luminexresources.com/site/assets/files/5388/2019-q3-mda-lr.pdf</t>
         </is>
       </c>
     </row>
@@ -6341,256 +6517,279 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>坐标精度：近似（Mirador 西北 ~24 km）；无已披露资源量（资源量未查到）；2019 BHP 赚入（承诺投入 ~4</t>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Mirador 西北 ~24 km）；无已披露资源量（资源量未查到）；2019 BHP 赚入（承诺投入 ~4,200 万美元）；信源 https://www.spglobal.com/marketintelligence/en/news-insights/trending/cqkcvo6oeefmcwpb56knea2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>AS-01</t>
+          <t>AS-71</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Nowa Sól</t>
+          <t>Cerro Moro</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Nowa Sól（Nowa Sól Project）</t>
+          <t>Cerro Moro</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>卢布斯卡省（Lubuskie）</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>51.61</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>15.14</v>
+          <t>圣克鲁斯省（Santa Cruz，Puerto Deseado 一带）</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>-48.03</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>-66.56</t>
+        </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>银</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>银、铅、锌</t>
+          <t>金</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Kupferschiefer 沉积型（沉积岩赋矿铜银）</t>
+          <t>低硫化浅成低温热液（low-sulphidation epithermal）</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>M&amp;I</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>603.9</t>
+          <t>约 2.7</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.24% Cu, 38.29 g/t Ag</t>
+          <t>约 250 g/t Ag、2 g/t Au</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>含铜 7.50 Mt、银 743.4 Moz</t>
+          <t>银约 22 Moz、金约 0.2 Moz（P&amp;P，口径待核实）</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>前 10 年 290 kt Cu + 28 Moz Ag/年</t>
+          <t>约 4.5-4.7 Moz Ag + 40-45 koz Au/年</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>波兰体系技术报告（非 NI 43-101）</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>Lumina Metals（TSX: LMCU）100%</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t>全球最大未开发银资源；PEA 税后（含 MET）NPV7 US$1.60B / IRR 10.8%；不含 MET NPV US$6.32B / IRR 18.0%；AISC US$1.17/lb；初始 CAPEX US$6.4B；平均埋深 1,950m。</t>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Puerto Deseado 一带）；并购所得（2023-03 Pan American 收购 Yamana Gold 获得，非 Beaty 原创、Beaty 已卸任董事长）；高品位银金地下矿；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>AS-02</t>
+          <t>AS-72</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Sulmierzyce</t>
+          <t>Jacobina</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Sulmierzyce</t>
+          <t>Jacobina</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>下西里西亚省（Dolnośląskie）</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>51.61</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>17.53</v>
+          <t>巴伊亚州（Bahia，Jacobina 市一带）</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>-11.2522</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>-40.5092</t>
+        </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>银</t>
-        </is>
-      </c>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Kupferschiefer 沉积型</t>
+          <t>条带状铁建造（BIF）赋矿金矿</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.09% Cu</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>含铜 6.44 Mt（推算）</t>
+          <t>金储量约 2.7 Moz、资源约 5 Moz（口径待核实）</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>未开发</t>
+          <t>约 190-200 koz Au/年（2024 年约 193 koz、2025 指引约 200 koz）</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>勘探</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>波兰体系技术报告</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>Lumina Metals 100%</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>推断资源量 308 Mt @ 2.09% Cu；拟 2027 年分拆；持续钻探/物探/建模。</t>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Jacobina 市）；并购所得（2023-03 收购 Yamana Gold 获得，Beaty 卸任后）；PAS 最大单体金矿、长期扩建至 250 koz/年；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>AS-03</t>
+          <t>AS-73</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mozów</t>
+          <t>El Peñon</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Mozów</t>
+          <t>El Peñon</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>智利</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>卢布斯卡省（Lubuskie）</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>15.41</v>
+          <t>安托法加斯塔大区（Antofagasta）</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>-24.67</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>-69.83</t>
+        </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -6600,12 +6799,12 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Kupferschiefer 沉积型</t>
+          <t>低硫化浅成低温热液（low-sulphidation epithermal）</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -6620,125 +6819,130 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>金储量约 1 Moz（口径待核实）</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>未开发</t>
+          <t>约 200 koz Au + 3.5 Moz Ag/年（2023 年约 201 koz Au / 3.6 Moz Ag，逐年递减）</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>勘探</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>Lumina Metals 100%</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>二手</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>早期勘探项目，尚无公开资源量。</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似；并购所得（2023-03 收购 Yamana Gold 获得，Beaty 卸任后）；智利老牌金银矿（原 Yamana 旗舰之一）；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>AS-04</t>
+          <t>AS-74</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Cangrejos</t>
+          <t>Timmins（Bell Creek + Timmins West）</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Cangrejos（+ Gran Bestia）</t>
+          <t>Timmins Complex</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>厄瓜多尔</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>埃尔奥罗省（El Oro）</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>-79.90000000000001</v>
+          <t>安大略省（Ontario，Timmins 地区）</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>48.552952</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>-81.178834</t>
+        </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>铜、银</t>
-        </is>
-      </c>
+      <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>金-铜斑岩（porphyry Au-Cu）</t>
+          <t>造山型/剪切带金矿（orogenic）</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>M&amp;I</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>0.55 g/t Au, 0.11% Cu</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>含金 16.8 Moz、铜约 2.6 Blb（M&amp;I）；Inferred 179 Mt → 2.2 Moz Au</t>
+          <t>未查到（口径待核实）</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>26 年露天矿，年均 371 koz Au + 41 Mlb Cu</t>
+          <t>约 120-140 koz Au/年</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>可研</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2023（PFS）</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -6748,100 +6952,109 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>洛阳钼业 CMOC</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>厄瓜多尔最大原生金矿；Probable 储量 659 Mt @ 0.55 g/t Au（11.6 Moz Au）；2023 PFS CAPEX US$925M；2025 年 CMOC 收购并签 US$17 亿采矿合同。</t>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Bell Creek 一带）；并购所得（2019-02 Pan American 收购 Tahoe Resources 获得，Beaty 任董事长期间）；含 Bell Creek 与 Timmins West 两座地下金矿，共用 Bell Creek 选厂；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>AS-05</t>
+          <t>AS-75</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Taca Taca</t>
+          <t>Shahuindo</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Taca Taca</t>
+          <t>Shahuindo</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>秘鲁</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>萨尔塔省（Salta）</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>-24.47</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>-68.25</v>
+          <t>卡哈马卡大区（Cajamarca，Cajabamba）</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>-7.6122</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>-78.2152</t>
+        </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>钼、金</t>
+          <t>银</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>铜-金-钼斑岩</t>
+          <t>氧化金矿（露天 + 堆浸）</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>M&amp;I</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>0.42% Cu, 0.09 g/t Au</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>含铜 8,716 kt、金 5,715 koz（M&amp;I）；P&amp;P 1,990 Mt → 8,429 kt Cu</t>
+          <t>未查到（口径待核实）</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>前 10 年 291 kt Cu/年、LOM 209 kt Cu/年</t>
+          <t>约 120-130 koz Au/年（2024 年约 128 koz）</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>可研</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
@@ -6851,70 +7064,79 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>First Quantum Minerals 100%</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>Beaty 2014 年售予 First Quantum；2020 首份储量（7.7Mt 铜）；2025-12 更新技术报告；ESIA 预计 2026 上半年获批。</t>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似；并购所得（2019-02 收购 Tahoe Resources 获得，Beaty 任董事长期间）；露天氧化金矿堆浸、低 AISC；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>AS-06</t>
+          <t>AS-76</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>San Jorge</t>
+          <t>Minera Florida</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>San Jorge</t>
+          <t>Minera Florida</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>智利</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>门多萨省（Mendoza）</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>-69.5</v>
+          <t>圣地亚哥大都会区（Metropolitana，Alhué）</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>-33.983333</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>-70.966667</t>
+        </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>金、钼</t>
+          <t>银、锌</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>铜-金-钼斑岩</t>
+          <t>低硫化浅成低温热液（low-sulphidation epithermal）</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>历史资源量</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -6929,125 +7151,130 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>未查到（口径待核实）</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>未开发</t>
+          <t>约 2,400-2,600 tpd 选厂；2026 指引约 25 koz Au + 66-71 万 oz Ag</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>勘探</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>历史非 43-101</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>未查到（曾归 Coro Mining）</t>
+          <t>Pan American Silver（100%）</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>二手</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>旧版 Lumina Copper 10 项目之一 → Global Copper → 新版 Lumina Copper；后售予 Coro Mining。资源量未查到。</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（Alhué）；并购所得（2023-03 收购 Yamana Gold 获得，Beaty 卸任后）；智利老牌金银锌地下矿；信源 https://panamericansilver.com/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>AS-07</t>
+          <t>AS-77</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Relincho</t>
+          <t>Musselwhite</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Relincho（今 NuevaUnión）</t>
+          <t>Musselwhite</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>智利</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>阿塔卡马大区（Atacama，Huasco 省）</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>-28.85</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>-70.15000000000001</v>
+          <t>安大略省（Ontario，Thunder Bay 以北约 500 km）</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>52.60</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>-90.40</t>
+        </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>钼、银</t>
-        </is>
-      </c>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>铜-钼-银斑岩</t>
+          <t>造山型金矿（石英脉，绿岩带/铁建造赋矿）</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>M&amp;I</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>0.23% Cu, 0.008% Mo</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>含铜 1,800 kt、钼 60 kt（M&amp;I）；P&amp;P 1,554 Mt → 5,412 kt Cu</t>
+          <t>金储量约 1.5 Moz + 资源约 0.506 Moz（口径待核实）</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>未开发（NuevaUnión 2018 完成预可研）</t>
+          <t>约 230-240 koz Au/年（2025 年 236,856 oz；2026 Equinox 归属 100-110 koz，8-12 月）</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>预可研</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
@@ -7057,276 +7284,299 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>Teck 50% / Newmont 50%（NuevaUnión JV）</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>与 El Morro 合并为 NuevaUnión；Beaty 2008 年随 Global Copper 售予 Teck。</t>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似；1997 年投产、累计产金超 6 Moz；2025-03 Orla 自 Newmont 收购，2026-07-31 随 Equinox-Orla 合并归入 Equinox；2026 AISC 指引 $1,700-1,800/oz；信源 https://www.equinoxgold.com/our-mines/musselwhite</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>AS-08</t>
+          <t>AS-78</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Galeno</t>
+          <t>Camino Rojo</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Galeno（El Galeno）</t>
+          <t>Camino Rojo（氧化物 + 地下硫化物）</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>秘鲁</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>卡哈马卡大区（Cajamarca，Yanacocha 矿区）</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>-7.03</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>-78.34999999999999</v>
+          <t>萨卡特卡斯州（Zacatecas，Mazapil 市 San Tiburcio）</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>24.19</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>-101.52</t>
+        </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>金、钼、银</t>
+          <t>银、锌</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>安第斯斑岩铜矿</t>
+          <t>卡林型/浸染状金-银（碳酸盐岩赋矿）+ 深部硫化物</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>M&amp;I</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>0.48% Cu, 0.11 g/t Au, 0.014% Mo</t>
+          <t>0.73 g/t Au、14.5 g/t Ag</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>含铜 8.5 Blb（约 3.86 Mt）（M&amp;I）；Inferred 124 Mt @ 0.36% Cu</t>
+          <t>金 1.59 Moz、银 31.5 Moz（P&amp;P）；地下 M&amp;I 50.1 Mt @ 2.45 g/t Au、10.6 g/t Ag → 3.95 Moz Au</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>可研目标 144 kt Cu/年、LOM 20 年</t>
+          <t>氧化物约 94-100 koz Au + 500-600 koz Ag/年（露天堆浸）</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>可研</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2007-11（更新）</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101（历史）</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>中国五矿 60% / 江西铜业 40%</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>Beaty 2007 年随 Northern Peru Copper 售予五矿+江铜；2013 年起搁置，近年重启技术评估。</t>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（UTM 14N 244150E/2675900N 换算）；2017 Orla 自 Goldcorp 收购、2021-12 首金、2022-04 商业生产，2026-07-31 随合并归入 Equinox；另有地下硫化物 M&amp;I 3.95 Moz Au 待开发；信源 https://www.sec.gov/Archives/edgar/data/1680056/000110465926031272/tm268794d1_ex99-1.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>AS-09</t>
+          <t>AS-79</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Hilorico</t>
+          <t>La Libertad</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Hilorico</t>
+          <t>La Libertad Mine &amp; Mill（Nicaragua Operations）</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>秘鲁</t>
+          <t>尼加拉瓜</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>卡哈马卡大区（Cajamarca，距 Galeno 1km）</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>-78.34</v>
+          <t>琼塔莱斯省（Chontales，马那瓜以东约 110 km）</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>12.22</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>-85.17</t>
+        </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>银、锌、铅</t>
-        </is>
-      </c>
+      <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>浅成低温热液（epithermal）</t>
+          <t>低硫化浅成低温热液（epithermal，脉状）</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>未查到</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>0.65 g/t Au, 3.3 g/t Ag（氧化物）</t>
+          <t>3.59 g/t Au</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>含金约 400 koz（氧化物推断）</t>
+          <t>金储量 431 koz（La Libertad 单矿；Nicaragua 综合体 1,169 koz @ 4.01 g/t）</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>未开发</t>
+          <t>综合体 2026 指引 200-250 koz Au/年（Libertad 选厂 2.25 Mtpa）</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>勘探</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>历史非 43-101</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>中国五矿/江西铜业（随 Northern Peru）</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>二手</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>浅成低温热液金矿，深部见高品位锌-银带。</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似；2009 年起连续生产；2019 Calibre 自 B2Gold 收购、2025-06-17 随 Calibre 合并归入 Equinox；hub-and-spoke 模式与 El Limon/Pavon/Eastern Borosi 共享 Libertad 选厂；信源 https://www.equinoxgold.com/our-mines/libertad-gold-mine/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AS-10</t>
+          <t>AS-80</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Pashpap</t>
+          <t>El Limon</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pashpap</t>
+          <t>El Limon Mine &amp; Mill（Nicaragua Operations）</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>秘鲁</t>
+          <t>尼加拉瓜</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>安卡什大区（Ancash）</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>-77.90000000000001</v>
+          <t>莱昂/奇南德加交界（León/Chinandega，莱昂东北约 38 km）</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>12.76</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>-86.75</t>
+        </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>金</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>锌</t>
+          <t>银</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>低硫化浅成低温热液（low-sulphidation epithermal）</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>储量</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -7341,76 +7591,81 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>金储量含于 Nicaragua 综合体（1,169 koz @ 4.01 g/t）</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>未开发</t>
+          <t>综合体 2026 指引 200-250 koz Au/年（El Limon 选厂 500 ktpa）</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>勘探</t>
+          <t>生产</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>NI 43-101</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>未查到（随 Northern Peru）</t>
+          <t>Equinox Gold（100%）</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>二手</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>Northern Peru Copper 早期铜-锌项目，无公开资源量。</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>坐标精度：近似（UTM 16N 529113E/1410396N 换算）；2009 年起连续生产、累计产金超 3 Moz；2019 Calibre 自 B2Gold 收购、2025-06-17 随 Calibre 合并归入 Equinox；含 Limon Central 露天 + Santa Pancha/Panteon/Veta Nueva 地下；信源 https://www.equinoxgold.com/our-mines/libertad-gold-mine/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AS-11</t>
+          <t>AS-01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Regalito / Caserones</t>
+          <t>Nowa Sól</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Caserones 矿（原 Regalito）</t>
+          <t>Nowa Sól（Nowa Sól Project）</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>智利</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>阿塔卡马大区（Atacama，III 区）</t>
+          <t>卢布斯卡省（Lubuskie）</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-28.07</v>
+        <v>51.61</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-69.45</v>
+        <v>15.14</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -7419,101 +7674,106 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>钼</t>
+          <t>银、铅、锌</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>斑岩铜-钼</t>
+          <t>Kupferschiefer 沉积型（沉积岩赋矿铜银）</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>储量</t>
+          <t>M&amp;I</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>603.9</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>0.31% Cu, 0.01% Mo</t>
+          <t>1.24% Cu, 38.29 g/t Ag</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>含铜 2,717 kt、钼 94 kt（P&amp;P）；M&amp;I 1,502 Mt @ 0.28% Cu → 4,279 kt Cu</t>
+          <t>含铜 7.50 Mt、银 743.4 Moz</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>2025 年产铜约 133 kt（Lundin 口径，AISC $2.54/lb）</t>
+          <t>前 10 年 290 kt Cu + 28 Moz Ag/年</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>生产</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>NI 43-101</t>
+          <t>波兰体系技术报告（非 NI 43-101）</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>Lundin Mining 51% / JX Nippon 30% 等</t>
+          <t>Lumina Metals（TSX: LMCU）100%</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>Beaty 2006 年以 US$1.37 亿售予 Pan Pacific Copper；2013 首产阴极铜、2014 产精矿；2023 Lundin 收购 51%。</t>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>全球最大未开发银资源；PEA 税后（含 MET）NPV7 US$1.60B / IRR 10.8%；不含 MET NPV US$6.32B / IRR 18.0%；AISC US$1.17/lb；初始 CAPEX US$6.4B；平均埋深 1,950m。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AS-12</t>
+          <t>AS-02</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Hushamu</t>
+          <t>Sulmierzyce</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Hushamu</t>
+          <t>Sulmierzyce</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>不列颠哥伦比亚省（BC，温哥华岛）</t>
+          <t>下西里西亚省（Dolnośląskie）</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>50.6</v>
+        <v>51.61</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>-127.5</v>
+        <v>17.53</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -7522,32 +7782,32 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>金、钼</t>
+          <t>银</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>斑岩铜-金-钼</t>
+          <t>Kupferschiefer 沉积型</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>历史资源量</t>
+          <t>Inferred</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>308</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>2.09% Cu</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>含铜 6.44 Mt（推算）</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -7562,61 +7822,66 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>历史非 43-101</t>
+          <t>波兰体系技术报告</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>Lumina Metals 100%</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>二手</t>
+          <t>是</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>Lumina Resources 资产（铜-金-钼）；资源量为历史口径、未查到现行值。</t>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>推断资源量 308 Mt @ 2.09% Cu；拟 2027 年分拆；持续钻探/物探/建模。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AS-13</t>
+          <t>AS-03</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Redstone</t>
+          <t>Mozów</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Redstone</t>
+          <t>Mozów</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>不列颠哥伦比亚省（BC）</t>
+          <t>卢布斯卡省（Lubuskie）</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>50.3</v>
+        <v>51.98</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-127.3</v>
+        <v>15.41</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -7625,17 +7890,17 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>镍</t>
+          <t>银</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>铜-镍</t>
+          <t>Kupferschiefer 沉积型</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>历史资源量</t>
+          <t>无</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -7670,130 +7935,1220 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>历史非 43-101</t>
+          <t>无</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>未查到</t>
+          <t>Lumina Metals 100%</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
           <t>二手</t>
         </is>
       </c>
-      <c r="U49" s="3" t="inlineStr">
-        <is>
-          <t>Lumina Resources 资产（铜-镍）；资源量为历史口径。</t>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>早期勘探项目，尚无公开资源量。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>AS-04</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cangrejos</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Cangrejos（+ Gran Bestia）</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>厄瓜多尔</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>埃尔奥罗省（El Oro）</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-79.90000000000001</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>铜、银</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>金-铜斑岩（porphyry Au-Cu）</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;I</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>0.55 g/t Au, 0.11% Cu</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>含金 16.8 Moz、铜约 2.6 Blb（M&amp;I）；Inferred 179 Mt → 2.2 Moz Au</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>26 年露天矿，年均 371 koz Au + 41 Mlb Cu</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>可研</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>2023（PFS）</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>NI 43-101</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>洛阳钼业 CMOC</t>
+        </is>
+      </c>
+      <c r="T50" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>厄瓜多尔最大原生金矿；Probable 储量 659 Mt @ 0.55 g/t Au（11.6 Moz Au）；2023 PFS CAPEX US$925M；2025 年 CMOC 收购并签 US$17 亿采矿合同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>AS-05</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Taca Taca</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Taca Taca</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>阿根廷</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>萨尔塔省（Salta）</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-68.25</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>钼、金</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>铜-金-钼斑岩</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;I</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>0.42% Cu, 0.09 g/t Au</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>含铜 8,716 kt、金 5,715 koz（M&amp;I）；P&amp;P 1,990 Mt → 8,429 kt Cu</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>前 10 年 291 kt Cu/年、LOM 209 kt Cu/年</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>可研</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>NI 43-101</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>First Quantum Minerals 100%</t>
+        </is>
+      </c>
+      <c r="T51" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>Beaty 2014 年售予 First Quantum；2020 首份储量（7.7Mt 铜）；2025-12 更新技术报告；ESIA 预计 2026 上半年获批。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>AS-06</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>San Jorge</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>San Jorge</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>阿根廷</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>门多萨省（Mendoza）</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-69.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>金、钼</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>铜-金-钼斑岩</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>历史资源量</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>未开发</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>勘探</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>历史非 43-101</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>未查到（曾归 Coro Mining）</t>
+        </is>
+      </c>
+      <c r="T52" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>二手</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>旧版 Lumina Copper 10 项目之一 → Global Copper → 新版 Lumina Copper；后售予 Coro Mining。资源量未查到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>AS-07</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Relincho</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Relincho（今 NuevaUnión）</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>智利</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>阿塔卡马大区（Atacama，Huasco 省）</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>-28.85</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>-70.15000000000001</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>钼、银</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>铜-钼-银斑岩</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;I</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>0.23% Cu, 0.008% Mo</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>含铜 1,800 kt、钼 60 kt（M&amp;I）；P&amp;P 1,554 Mt → 5,412 kt Cu</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>未开发（NuevaUnión 2018 完成预可研）</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>预可研</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>NI 43-101</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>Teck 50% / Newmont 50%（NuevaUnión JV）</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>与 El Morro 合并为 NuevaUnión；Beaty 2008 年随 Global Copper 售予 Teck。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>AS-08</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Galeno</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Galeno（El Galeno）</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>卡哈马卡大区（Cajamarca，Yanacocha 矿区）</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>-7.03</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-78.34999999999999</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>金、钼、银</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>安第斯斑岩铜矿</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;I</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>0.48% Cu, 0.11 g/t Au, 0.014% Mo</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>含铜 8.5 Blb（约 3.86 Mt）（M&amp;I）；Inferred 124 Mt @ 0.36% Cu</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>可研目标 144 kt Cu/年、LOM 20 年</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>可研</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2007-11（更新）</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>NI 43-101（历史）</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>中国五矿 60% / 江西铜业 40%</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>Beaty 2007 年随 Northern Peru Copper 售予五矿+江铜；2013 年起搁置，近年重启技术评估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>AS-09</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Hilorico</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Hilorico</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>卡哈马卡大区（Cajamarca，距 Galeno 1km）</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>-78.34</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>银、锌、铅</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>浅成低温热液（epithermal）</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>0.65 g/t Au, 3.3 g/t Ag（氧化物）</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>含金约 400 koz（氧化物推断）</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>未开发</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>勘探</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>历史非 43-101</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>中国五矿/江西铜业（随 Northern Peru）</t>
+        </is>
+      </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>二手</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>浅成低温热液金矿，深部见高品位锌-银带。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>AS-10</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Pashpap</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Pashpap</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>安卡什大区（Ancash）</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>锌</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>未开发</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>勘探</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>未查到（随 Northern Peru）</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>二手</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>Northern Peru Copper 早期铜-锌项目，无公开资源量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>AS-11</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Regalito / Caserones</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Caserones 矿（原 Regalito）</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>智利</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>阿塔卡马大区（Atacama，III 区）</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>-28.07</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>-69.45</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>钼</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>斑岩铜-钼</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>储量</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>0.31% Cu, 0.01% Mo</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>含铜 2,717 kt、钼 94 kt（P&amp;P）；M&amp;I 1,502 Mt @ 0.28% Cu → 4,279 kt Cu</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>2025 年产铜约 133 kt（Lundin 口径，AISC $2.54/lb）</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>生产</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>NI 43-101</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>Lundin Mining 51% / JX Nippon 30% 等</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>一手</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>Beaty 2006 年以 US$1.37 亿售予 Pan Pacific Copper；2013 首产阴极铜、2014 产精矿；2023 Lundin 收购 51%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>AS-12</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Hushamu</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Hushamu</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>不列颠哥伦比亚省（BC，温哥华岛）</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-127.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>金、钼</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>斑岩铜-金-钼</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>历史资源量</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>未开发</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>勘探</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>历史非 43-101</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>二手</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>Lumina Resources 资产（铜-金-钼）；资源量为历史口径、未查到现行值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>AS-13</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Redstone</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Redstone</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>不列颠哥伦比亚省（BC）</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-127.3</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>镍</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>铜-镍</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>历史资源量</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>未开发</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>勘探</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>历史非 43-101</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>二手</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>Lumina Resources 资产（铜-镍）；资源量为历史口径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>AS-14</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>权益金组合（4 项 NSR）</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Lumina Royalty Portfolio</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>智利/阿根廷</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>-25</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G60" s="3" t="n">
         <v>-69</v>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>铜</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>钼</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>NSR 权益金</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="P60" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
+      <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="S50" s="3" t="inlineStr">
+      <c r="S60" s="3" t="inlineStr">
         <is>
           <t>Franco-Nevada</t>
         </is>
       </c>
-      <c r="T50" s="3" t="inlineStr">
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
         <is>
           <t>一手</t>
         </is>
       </c>
-      <c r="U50" s="3" t="inlineStr">
+      <c r="V60" s="3" t="inlineStr">
         <is>
           <t>Relincho 1.5%、Taca Taca 1.08%、San Jorge、Vizcachitas 四项 NSR；2011 年 US$66M 售予 Franco-Nevada。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U50"/>
+  <autoFilter ref="A1:V60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8629,7 +9984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9660,17 +11015,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CO-17</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>AS-01</t>
+          <t>AS-71</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>旗舰</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -9688,12 +11043,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CO-17</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AS-02</t>
+          <t>AS-72</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -9716,12 +11071,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CO-17</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>AS-03</t>
+          <t>AS-73</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9744,17 +11099,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CO-15</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>AS-04</t>
+          <t>AS-74</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>旗舰</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -9772,17 +11127,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CO-09</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>AS-05</t>
+          <t>AS-75</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>旗舰</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -9800,12 +11155,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CO-09</t>
+          <t>CO-03</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>AS-06</t>
+          <t>AS-76</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9828,17 +11183,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CO-08</t>
+          <t>CO-13</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>AS-07</t>
+          <t>AS-77</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>旗舰</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -9856,17 +11211,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CO-07</t>
+          <t>CO-13</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>AS-08</t>
+          <t>AS-78</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>旗舰</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -9884,12 +11239,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CO-07</t>
+          <t>CO-13</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>AS-09</t>
+          <t>AS-79</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -9912,12 +11267,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CO-07</t>
+          <t>CO-13</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>AS-10</t>
+          <t>AS-80</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -9940,12 +11295,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CO-05</t>
+          <t>CO-17</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>AS-11</t>
+          <t>AS-01</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -9968,12 +11323,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CO-06</t>
+          <t>CO-17</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>AS-12</t>
+          <t>AS-02</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -9996,12 +11351,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CO-06</t>
+          <t>CO-17</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>AS-13</t>
+          <t>AS-03</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -10024,17 +11379,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CO-10</t>
+          <t>CO-15</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>AS-14</t>
+          <t>AS-04</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>次要</t>
+          <t>旗舰</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -10052,17 +11407,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CO-18</t>
+          <t>CO-09</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>AS-45</t>
+          <t>AS-05</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>次要（当前权属）</t>
+          <t>旗舰</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -10070,11 +11425,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>2006-2009</t>
-        </is>
-      </c>
+      <c r="F51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -10084,17 +11435,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CO-12</t>
+          <t>CO-09</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>AS-63</t>
+          <t>AS-06</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>次要（Leagold 合并带入）</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -10102,11 +11453,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>2016-2020</t>
-        </is>
-      </c>
+      <c r="F52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -10121,12 +11468,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>AS-05</t>
+          <t>AS-07</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>次要（前手）</t>
+          <t>旗舰</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -10134,11 +11481,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>2005-2008</t>
-        </is>
-      </c>
+      <c r="F53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -10148,17 +11491,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CO-08</t>
+          <t>CO-07</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>AS-06</t>
+          <t>AS-08</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>次要（前手）</t>
+          <t>旗舰</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -10166,11 +11509,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>2005-2008</t>
-        </is>
-      </c>
+      <c r="F54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -10180,17 +11519,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CO-10</t>
+          <t>CO-07</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>AS-05</t>
+          <t>AS-09</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>NSR 1.08%</t>
+          <t>次要</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -10198,11 +11537,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -10212,32 +11547,332 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t>CO-07</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>AS-10</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>次要</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>RL-056</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>CO-05</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>AS-11</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>旗舰</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>RL-057</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>CO-06</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>AS-12</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>次要</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>RL-058</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CO-06</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>AS-13</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>次要</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>RL-059</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>CO-10</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>AS-14</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>次要</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>RL-060</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CO-18</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>AS-45</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>次要（当前权属）</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>2006-2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>RL-061</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>CO-12</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>AS-63</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>次要（Leagold 合并带入）</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>2016-2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>RL-062</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>CO-08</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>AS-05</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>次要（前手）</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>2005-2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>RL-063</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>CO-08</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>AS-06</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>次要（前手）</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>2005-2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>RL-064</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>CO-10</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>AS-05</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>NSR 1.08%</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>RL-065</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>CO-10</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>AS-07</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>NSR 1.5%</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F56"/>
+  <autoFilter ref="A1:F66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
